--- a/output/pdf_financials_xlsx/SRR.xlsx
+++ b/output/pdf_financials_xlsx/SRR.xlsx
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>3.334391</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>4.811073</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>5.654065</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>4.380296</v>
       </c>
     </row>
     <row r="11">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">

--- a/output/pdf_financials_xlsx/SRR.xlsx
+++ b/output/pdf_financials_xlsx/SRR.xlsx
@@ -535,15 +535,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -601,15 +597,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -630,15 +622,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -659,15 +647,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -688,15 +672,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>6.606067</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4.396747</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3.334391</v>
@@ -754,15 +734,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -783,15 +759,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -812,15 +784,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -841,15 +809,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -870,15 +834,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-7.600357</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.133817</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>3.442711</v>
@@ -899,21 +859,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>2.370039</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.310358</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.286583</v>
+        <v>-0.884657</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.431356</v>
+        <v>-0.700299</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.676994</v>
@@ -1002,15 +958,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-5.230318</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.134773</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>3.156128</v>
@@ -1031,15 +983,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1060,15 +1008,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1089,15 +1033,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-5.230318</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.134773</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>3.156128</v>
@@ -1118,15 +1058,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0.06</v>
@@ -1147,15 +1083,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.006</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0.059</v>
@@ -1176,15 +1108,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>29.001311</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>31.210964</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>43.218505</v>
@@ -1205,15 +1133,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-7.600357</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.133817</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3.442711</v>
@@ -1234,15 +1158,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1263,15 +1183,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-7.600357</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.133817</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3.442711</v>
@@ -1329,21 +1245,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-31.1832588916547</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-231.9271841395338</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.324340904595246</v>
+        <v>25.69652230466048</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19.03089593308771</v>
+        <v>30.89633015663487</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>31.16466181438863</v>
@@ -3033,15 +2945,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-2.856327</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>0.176541</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>2.558054</v>
@@ -3062,15 +2970,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -3091,15 +2995,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.127291</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.447907</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.272273</v>
@@ -3120,15 +3020,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -3149,15 +3045,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.020952</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.021047</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>-0.03917</v>
@@ -3178,15 +3070,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.005768</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.0454</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>-0.097529</v>
@@ -3207,15 +3095,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -3236,15 +3120,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.112107</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.38146</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.408972</v>
@@ -3265,15 +3145,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.266188</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.313704</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0.399453</v>
@@ -3294,15 +3170,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -3323,15 +3195,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -3352,15 +3220,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3381,15 +3245,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3410,15 +3270,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -3439,15 +3295,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -3468,15 +3320,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -3497,15 +3345,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -3526,15 +3370,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -3555,15 +3395,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -3584,15 +3420,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -3613,15 +3445,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.684864</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-1.193555</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>-3.616536</v>
@@ -3642,15 +3470,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -3671,15 +3495,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -3700,15 +3520,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -3729,15 +3545,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -3758,15 +3570,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3787,15 +3595,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3816,15 +3620,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -3882,15 +3682,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>-1.376112</v>
@@ -3911,15 +3707,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.863815</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>-1.633294</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>9.960792</v>
@@ -3940,15 +3732,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.316711</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.91356</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>1.492322</v>
@@ -3969,15 +3757,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -3998,15 +3782,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.403151</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.578762</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>11.66018</v>
@@ -4027,15 +3807,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.91356</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1.492322</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>13.152502</v>
@@ -4056,15 +3832,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -4085,15 +3857,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>1.145528</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>3.405611</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>5.315924</v>
@@ -4119,7 +3887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5986,10 +5754,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F43" s="5" t="n">
+        <v>0.176541</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>2.558054</v>
@@ -6116,7 +5882,11 @@
           <t>Deferred income taxes recovery (note 11)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6165,15 +5935,11 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="5" t="n">
+        <v>0.127291</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-0.447907</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>-0.272273</v>
@@ -6209,15 +5975,11 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>-0.020952</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.021047</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>-0.03917</v>
@@ -6253,15 +6015,11 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>0.005768</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.0454</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>-0.097529</v>
@@ -6298,10 +6056,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>0.08230800000000001</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>0.59619</v>
@@ -6337,15 +6093,11 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="5" t="n">
+        <v>1.145528</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>3.405611</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>5.315924</v>
@@ -6563,25 +6315,19 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>-0.863815</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-1.633294</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H56" s="5" t="n">
+        <v>-3.325894</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>-3.447791</v>
@@ -6705,15 +6451,11 @@
           <t>InvestingCashFlow</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="5" t="n">
+        <v>-0.684864</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-1.193555</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>-3.616536</v>
@@ -6754,10 +6496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F60" s="5" t="n">
+        <v>0.578762</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>11.66018</v>
@@ -6793,15 +6533,11 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="5" t="n">
+        <v>1.316711</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.91356</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>1.492322</v>
@@ -6837,15 +6573,11 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="5" t="n">
+        <v>0.91356</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1.492322</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>13.152502</v>
@@ -6886,10 +6618,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="5" t="n">
+        <v>0.313704</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>0.399453</v>
@@ -6897,10 +6627,8 @@
       <c r="H63" s="5" t="n">
         <v>0.775266</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="5" t="n">
+        <v>0.840311</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6929,15 +6657,11 @@
           <t>Depletion</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>1.036501</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>2.235533</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>2.181041</v>
@@ -6945,10 +6669,8 @@
       <c r="H64" s="5" t="n">
         <v>3.182685</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="5" t="n">
+        <v>3.940341</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6972,7 +6694,11 @@
           <t>Deferred income taxes expense (recovery) (note 10)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6989,10 +6715,8 @@
       <c r="H65" s="5" t="n">
         <v>0.129357</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="5" t="n">
+        <v>-0.2816</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -7017,15 +6741,11 @@
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>-0.863815</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-1.469014</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>-2.020348</v>
@@ -7033,10 +6753,8 @@
       <c r="H66" s="5" t="n">
         <v>-3.37105</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="5" t="n">
+        <v>-3.449041</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -7144,37 +6862,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Return of capital (note 8e)</t>
+          <t>Purchase of petroleum and natural gas interests (note 5)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>-0.434864</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-1.193555</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.443438</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.616536</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>-13.277475</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-0.027103</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -7195,7 +6905,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Proceeds from shares issued (note 8a)</t>
+          <t>Return of capital (note 8e)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7210,7 +6920,7 @@
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>13.494008</v>
+        <v>-0.443438</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7241,10 +6951,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Proceeds from warrants issued (note 8a)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Proceeds from shares issued (note 8a)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7256,7 +6970,7 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.306682</v>
+        <v>13.494008</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -7287,14 +7001,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Proceeds from warrants issued (note 8a)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7306,7 +7016,7 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-1.376112</v>
+        <v>0.306682</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -7337,12 +7047,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) financing activities</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7356,10 +7066,12 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>9.960792</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>-3.325894</v>
+        <v>-1.376112</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -7380,30 +7092,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Purchase of petroleum and natural gas interests (note 5)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>-1.633294</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-3.616536</v>
+        <v>9.960792</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-13.277475</v>
+        <v>-3.325894</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -7419,25 +7133,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Royalty revenues (note 10) $</t>
+          <t>Impairment (note 5)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>4.905855</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>1.381559</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7449,122 +7163,128 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>7.689586</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>6.03113</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Bad debt (recovery)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.753897</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0.853122</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>0.873413</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>0.769099</v>
+      <c r="F76" s="5" t="n">
+        <v>-0.009908</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share-based compensation (notes 9c and 9d)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Deferred income taxes (recovery) (note 10)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="5" t="n">
+        <v>-0.392666</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-0.009842</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0.840311</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>0.648705</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Depletion (note 6)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Depletion</t>
-        </is>
-      </c>
+          <t>Return of capital (note 8a)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -7575,97 +7295,97 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" s="5" t="n">
+        <v>-0.443438</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n">
-        <v>3.940341</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>2.962492</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Deferred Financing Costs (note 8d)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>3.334391</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>4.811073</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>5.654065</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>4.380296</v>
+      <c r="F79" s="5" t="n">
+        <v>-0.16428</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Income for the year</t>
+          <t>Net income (loss) $</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-2.856327</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.176541</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -7677,158 +7397,176 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>2.035521</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>1.650834</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Interest on cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.286583</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.431356</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0.136792</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>0.126978</v>
+          <t>Share-based compensation (notes 7 and 8c)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.266188</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.313704</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Income before taxes</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>3.442711</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>2.266609</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>2.172313</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>1.777812</v>
+          <t>Bad Debt (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>0.051242</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.009908</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Current tax expense</t>
+          <t>Deferred income taxes (recovery) expense (note 10)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.894499</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>0.5709419999999999</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>0.9585939999999999</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>0.543046</v>
+      <c r="E83" s="5" t="n">
+        <v>-2.370038</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.392666</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Deferred tax recovery</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Purchase of intangibles (note 6)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7845,43 +7583,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n">
-        <v>-0.2816</v>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>-0.087726</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Income tax expense (note 11)</t>
+          <t>Increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>-0.403151</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.578762</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7893,11 +7631,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n">
-        <v>0.676994</v>
-      </c>
-      <c r="J85" s="5" t="n">
-        <v>0.45532</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -7906,14 +7648,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Total comprehensive income $</t>
+          <t>Royalty revenues (note 10) $</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -7927,17 +7665,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="5" t="n">
-        <v>2.558054</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>1.56631</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I86" s="5" t="n">
-        <v>1.495319</v>
+        <v>7.689586</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>1.322492</v>
+        <v>6.03113</v>
       </c>
     </row>
     <row r="87">
@@ -7948,44 +7690,36 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Income per share, basic (note 9) $</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.346281</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.475859</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.753897</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.853122</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>3.3e-08</v>
+        <v>0.873413</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>2.9e-08</v>
+        <v>0.769099</v>
       </c>
     </row>
     <row r="88">
@@ -7996,19 +7730,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Income per share, diluted (note 9) $</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Share-based compensation (notes 9c and 9d)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -8030,10 +7760,10 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>3.1e-08</v>
+        <v>0.840311</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>2.8e-08</v>
+        <v>0.648705</v>
       </c>
     </row>
     <row r="89">
@@ -8044,17 +7774,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Depletion (note 6)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>Depletion</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8067,17 +7797,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G89" s="5" t="n">
-        <v>42.344911</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>45.02214</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>45.386449</v>
+        <v>3.940341</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>45.582727</v>
+        <v>2.962492</v>
       </c>
     </row>
     <row r="90">
@@ -8088,40 +7822,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>6.606067</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>4.396747</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>43.218505</v>
+        <v>3.334391</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>46.579059</v>
+        <v>4.811073</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>47.769195</v>
+        <v>5.654065</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>48.00292</v>
+        <v>4.380296</v>
       </c>
     </row>
     <row r="91">
@@ -8132,15 +7862,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Share capital       Warrants          surplus              Deficit               equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>As at December 31, 2023 $ 26,478,588 $ 306,682 $ 16,765,055 $</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Income for the year</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8156,16 +7890,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H91" s="5" t="n">
+        <v>1.835253</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>26.857137</v>
+        <v>2.035521</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-16.693188</v>
+        <v>1.650834</v>
       </c>
     </row>
     <row r="92">
@@ -8176,12 +7908,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Share capital       Warrants          surplus              Deficit               equity</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Warrants (note 9a and 9b) 1,290 (306,682) 306,642</t>
+          <t>Interest on cash and cash equivalents</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8195,23 +7927,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G92" s="5" t="n">
+        <v>0.286583</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.431356</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.136792</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.126978</v>
       </c>
     </row>
     <row r="93">
@@ -8222,15 +7948,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Income before taxes</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -8241,23 +7971,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>3.442711</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>2.266609</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.840311</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.172313</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>1.777812</v>
       </c>
     </row>
     <row r="94">
@@ -8266,10 +7990,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RSU vesting 282,219 - (282,219)</t>
+          <t>Current tax expense</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8278,30 +8006,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" s="5" t="n">
+        <v>0.08230800000000001</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.894499</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.5709419999999999</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0.9585939999999999</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.543046</v>
       </c>
     </row>
     <row r="95">
@@ -8310,27 +8028,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dividends (note 9e) - - -</t>
+          <t>Deferred tax recovery</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="5" t="n">
+        <v>-2.370038</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.392666</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.009842</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -8338,10 +8054,10 @@
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-3.473939</v>
+        <v>-0.2816</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>-3.473939</v>
+        <v>-0.087726</v>
       </c>
     </row>
     <row r="96">
@@ -8352,15 +8068,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Income tax expense (note 11)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8382,10 +8102,10 @@
         </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>1.495319</v>
+        <v>0.676994</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>1.495319</v>
+        <v>0.45532</v>
       </c>
     </row>
     <row r="97">
@@ -8396,12 +8116,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>As at December 31, 2024 $ 26,762,097 - $ 17,629,789 $</t>
+          <t>Total comprehensive income $</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -8410,26 +8130,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>0.176541</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>2.558054</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1.56631</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>25.720078</v>
+        <v>1.495319</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>-18.671808</v>
+        <v>1.322492</v>
       </c>
     </row>
     <row r="98">
@@ -8438,13 +8152,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RSU and option settlement - - (715,051)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Income per share, basic (note 9) $</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8466,12 +8188,10 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.715051</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.3e-08</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>2.9e-08</v>
       </c>
     </row>
     <row r="99">
@@ -8482,15 +8202,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>for the year</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>As at December 31, 2025 $ 26,762,097 - 17,563,443</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Income per share, diluted (note 9) $</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8512,10 +8236,10 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>23.420772</v>
+        <v>3.1e-08</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-20.904768</v>
+        <v>2.8e-08</v>
       </c>
     </row>
     <row r="100">
@@ -8524,38 +8248,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Royalty revenues (note 9) $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>29.001311</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>29.422055</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>6.490519</v>
+        <v>42.344911</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>6.646326</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45.02214</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>45.386449</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>45.582727</v>
       </c>
     </row>
     <row r="101">
@@ -8566,40 +8290,36 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share-based compensation (notes 8c and 8d)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>29.001311</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>31.210964</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.399453</v>
+        <v>43.218505</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.775266</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46.579059</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>47.769195</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>48.00292</v>
       </c>
     </row>
     <row r="102">
@@ -8610,19 +8330,15 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share capital       Warrants          surplus              Deficit               equity</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Depletion (note 5)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Depletion</t>
-        </is>
-      </c>
+          <t>As at December 31, 2023 $ 26,478,588 $ 306,682 $ 16,765,055 $</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8633,21 +8349,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" s="5" t="n">
-        <v>2.181041</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>3.182685</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>26.857137</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-16.693188</v>
       </c>
     </row>
     <row r="103">
@@ -8658,19 +8374,15 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share capital       Warrants          surplus              Deficit               equity</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Warrants (note 9a and 9b) 1,290 (306,682) 306,642</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -8681,16 +8393,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" s="5" t="n">
-        <v>3.156128</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>1.835253</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.00125</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -8706,12 +8420,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Deferred tax expense (recovery)</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8725,16 +8439,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="5" t="n">
-        <v>-0.009842</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.129357</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.776909</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.840311</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -8748,14 +8462,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Income tax recovery (note 10)</t>
+          <t>RSU vesting 282,219 - (282,219)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8769,11 +8479,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" s="5" t="n">
-        <v>0.884657</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.700299</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -8792,21 +8506,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Income per share, basic $</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Dividends (note 9e) - - -</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8817,21 +8523,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="5" t="n">
-        <v>5.999999999999999e-08</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>3.5e-08</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>-3.473939</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>-3.473939</v>
       </c>
     </row>
     <row r="107">
@@ -8842,19 +8548,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Income per share, diluted $</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8865,21 +8567,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="5" t="n">
-        <v>5.9e-08</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>3.4e-08</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.56631</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>1.495319</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>1.495319</v>
       </c>
     </row>
     <row r="108">
@@ -8890,12 +8590,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Share capital       Warrants         surplus              Deficit             equity</t>
+          <t>for the year</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>As at December 31, 2021 $ 13,984,321 $ - $ 15,731,541 $</t>
+          <t>As at December 31, 2024 $ 26,762,097 - $ 17,629,789 $</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8909,21 +8609,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G108" s="5" t="n">
-        <v>14.561098</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>-15.154764</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>25.720078</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>-18.671808</v>
       </c>
     </row>
     <row r="109">
@@ -8932,14 +8632,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Shares issued for cash (note</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>8a) 13,494,008 - -</t>
+          <t>RSU and option settlement - - (715,051)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8953,18 +8649,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" s="5" t="n">
-        <v>13.494008</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="5" t="n">
+        <v>-0.715051</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -8980,12 +8676,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Shares issued for cash (note</t>
+          <t>for the year</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Warrants (note 8a) - 306,682 -</t>
+          <t>As at December 31, 2025 $ 26,762,097 - 17,563,443</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8999,23 +8695,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" s="5" t="n">
-        <v>0.306682</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="5" t="n">
+        <v>23.420772</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>-20.904768</v>
       </c>
     </row>
     <row r="111">
@@ -9024,39 +8718,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Share issuance costs, net of</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Share issuance costs, net of deferred tax benefit of $354,290 (1,186,102) - -</t>
+          <t>Royalty revenues (note 9) $</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="5" t="n">
+        <v>1.375749</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>4.261974</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-1.186102</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.490519</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>6.646326</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>7.689586</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -9072,12 +8754,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>(note 8c and 8d) - - 399,453</t>
+          <t>Share-based compensation (notes 8c and 8d)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -9086,23 +8768,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="5" t="n">
+        <v>0.313704</v>
       </c>
       <c r="G112" s="5" t="n">
         <v>0.399453</v>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>0.775266</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0.840311</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -9118,35 +8794,33 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dividends (note 8e) - - -</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depletion (note 5)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Depletion</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>1.036501</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>2.235533</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>-2.693798</v>
+        <v>2.181041</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>-2.693798</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.182685</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>3.940341</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -9162,12 +8836,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year - - -</t>
+          <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -9182,15 +8856,13 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2.558054</v>
+        <v>-0.009842</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>2.558054</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.129357</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>-0.2816</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -9206,35 +8878,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>As at December 31, 2022 $ 26,292,227 $ 306,682 $ 16,130,994 $</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income tax recovery (note 10)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>-2.370039</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>-0.310358</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>27.439395</v>
+        <v>0.884657</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>-15.290508</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.700299</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.676994</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -9250,15 +8920,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>(note 8c and 8d) - - 776,909</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Income per share, basic (note 8) $</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9269,18 +8943,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G116" s="5" t="n">
-        <v>0.776909</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>3.5e-08</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>3.3e-08</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -9296,15 +8968,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Provision for income taxes</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stock Option/RSU Exercise 186,361 - (142,848)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Income per share, diluted (note 8) $</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9315,18 +8991,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>0.043513</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>3.4e-08</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>3.1e-08</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -9342,12 +9016,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Share capital       Warrants         surplus             Deficit             equity</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>As at December 31, 2023 $ 26,478,588 $ 306,682 $ 16,765,055 $</t>
+          <t>As at December 31, 2022 $ 26,292,227 $ 306,682 $ 16,130,994 $</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9361,18 +9035,2442 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>27.439395</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>-15.290508</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Stock Option/RSU exercise 186,361 - (142,848)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0.043513</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dividends (note 8e) - - -</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>-2.96899</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-2.96899</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>for the year</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>As at December 31, 2023 $ 26,478,588 $ 306,682 $ 16,765,055 $</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
         <v>26.857137</v>
       </c>
-      <c r="H118" s="5" t="n">
+      <c r="I121" s="5" t="n">
         <v>-16.693188</v>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>for the year</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Warrants (note 8a and 8b) 1,290 (306,682) 306,642</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>for the year</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>As at December 31, 2024 $ 26,762,097 - 17,629,789</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>25.720078</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>-18.671808</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-0.134773</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>3.156128</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>1.835253</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Income per share, basic $</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>6e-09</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>3.5e-08</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Income per share, diluted $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>6e-09</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>5.9e-08</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>3.4e-08</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Share capital       Warrants         surplus              Deficit             equity</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>As at December 31, 2021 $ 13,984,321 $ - $ 15,731,541 $</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>14.561098</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>-15.154764</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Shares issued for cash (note</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>8a) 13,494,008 - -</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>13.494008</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>13.494008</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Shares issued for cash (note</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Warrants (note 8a) - 306,682 -</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.306682</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.306682</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Share issuance costs, net of</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Share issuance costs, net of deferred tax benefit of $354,290 (1,186,102) - -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-1.186102</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-1.186102</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>(note 8c and 8d) - - 399,453</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.399453</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.399453</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dividends (note 8e) - - -</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>-2.693798</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>-2.693798</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year - - -</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>2.558054</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2.558054</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>2.558054</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>As at December 31, 2022 $ 26,292,227 $ 306,682 $ 16,130,994 $</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>27.439395</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>27.439395</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>-15.290508</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>(note 8c and 8d) - - 776,909</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.776909</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Stock Option/RSU Exercise 186,361 - (142,848)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.043513</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>As at December 31, 2023 $ 26,478,588 $ 306,682 $ 16,765,055 $</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>26.857137</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>-16.693188</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bad debt (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>0.051242</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.009908</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Impairment (note 5)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>4.905855</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>1.381559</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="5" t="n">
+        <v>0.003953</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.000956</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.286583</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Income (loss) before taxes</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-0.133817</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>3.442711</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Diluted total</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>31.210964</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>43.218505</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Share capital       Warrants         surplus              Deficit             equity</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>As at December 31, 2020 $ 28,679,325 $ - $ 1,081,271 $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>15.752069</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>-14.008527</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests (note 4) 85,000 - -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Return of capital (443,438) - -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-0.443438</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Reduction of stated capital (14,556,562) -</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>14.556562</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Shares issued for</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Shares issued for compensation (note 8c and 8d) 186,000 - 127,704</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.313704</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of stock options (note 8c) 33,996 -</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>-0.033996</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Dividends (note 8f) - - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-1.322778</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>-1.322778</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>-0.176541</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>-0.176541</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>As at December 31, 2021 $ 13,984,321 $ - $ 15,731,541 $</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>14.561098</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>-15.154764</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dividends (note 8f) - - -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>-2.693798</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>-2.693798</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Share-based compensation (notes 7 and 8c)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>0.266188</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.313704</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>-5.230318</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>-0.134773</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Loss before taxes</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" s="5" t="n">
+        <v>-5.226365</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>-0.133817</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Total comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" s="5" t="n">
+        <v>-2.856327</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.176541</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Income (loss) per share, basic $</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>-9.9e-08</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>6e-09</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Income (loss) per share, diluted $</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>-9.9e-08</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>6e-09</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Share capital        surplus              Deficit             equity</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>As at December 31, 2019 $ 28,556,354 $ 933,554 $</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" s="5" t="n">
+        <v>18.915889</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>-10.574019</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>(note 5) 4,500 -</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Shares issued for compensation (note 7 and 8c) 118,471 147,717</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>0.266188</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Dividends (note 8e) - -</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" s="5" t="n">
+        <v>-0.5781809999999999</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>-0.5781809999999999</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>-2.856327</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>-2.856327</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>As at December 31, 2020 $ 28,679,325 $ 1,081,271 $</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" s="5" t="n">
+        <v>15.752069</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>-14.008527</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>(note 5) 85,000 -</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" s="5" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Return of capital (note 8a) (443,438) -</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" s="5" t="n">
+        <v>-0.443438</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Reduction of stated capital (note 8a) (14,556,562) 14,556,562</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Shares issued on acquisition of royalty interests</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Shares issued for compensation (note 7 and 8c) 186,000 127,704</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" s="5" t="n">
+        <v>0.313704</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of stock options (note</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>8c) 33,996 (33,996)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of stock options (note</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dividends (note 8e) - -</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>-1.322778</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>-1.322778</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of stock options (note</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Total comprehensive income - -</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" s="5" t="n">
+        <v>0.176541</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>0.176541</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of stock options (note</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>As at December 31, 2021 $ 13,984,321 $ 15,731,541 $</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" s="5" t="n">
+        <v>14.561098</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>-15.154764</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
         <is>
           <t>-</t>
         </is>
